--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>283</v>
+        <v>208</v>
       </c>
       <c r="D2">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>330</v>
       </c>
       <c r="D3">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="E3">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>150</v>
+        <v>34</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="D2">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>81</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D3">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H3">
         <v>426</v>
